--- a/artfynd/A 36356-2025 artfynd.xlsx
+++ b/artfynd/A 36356-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,6 +1131,309 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129375967</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storöratjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552860</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6840003</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129374083</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79631</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storöratjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552860</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6840003</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129375970</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storöratjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552860</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6840003</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36356-2025 artfynd.xlsx
+++ b/artfynd/A 36356-2025 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>129375967</v>
       </c>
       <c r="B6" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129374083</v>
       </c>
       <c r="B7" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>129375970</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36356-2025 artfynd.xlsx
+++ b/artfynd/A 36356-2025 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>129375967</v>
       </c>
       <c r="B6" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129374083</v>
       </c>
       <c r="B7" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
         <v>129375970</v>
       </c>
       <c r="B8" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36356-2025 artfynd.xlsx
+++ b/artfynd/A 36356-2025 artfynd.xlsx
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 36356-2025 artfynd.xlsx
+++ b/artfynd/A 36356-2025 artfynd.xlsx
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 36356-2025 artfynd.xlsx
+++ b/artfynd/A 36356-2025 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>129375967</v>
       </c>
       <c r="B6" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129374083</v>
       </c>
       <c r="B7" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>129375970</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36356-2025 artfynd.xlsx
+++ b/artfynd/A 36356-2025 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>129375967</v>
       </c>
       <c r="B6" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129374083</v>
       </c>
       <c r="B7" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>129375970</v>
       </c>
       <c r="B8" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36356-2025 artfynd.xlsx
+++ b/artfynd/A 36356-2025 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>129375967</v>
       </c>
       <c r="B6" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129374083</v>
       </c>
       <c r="B7" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>129375970</v>
       </c>
       <c r="B8" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36356-2025 artfynd.xlsx
+++ b/artfynd/A 36356-2025 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>129375967</v>
       </c>
       <c r="B6" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129374083</v>
       </c>
       <c r="B7" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>129375970</v>
       </c>
       <c r="B8" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
